--- a/STR Loss.xlsx
+++ b/STR Loss.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Saif\Activation\Data\STR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079100AF-8797-4AF2-ACCD-69BAFF1D3142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15051C73-DC5D-4A32-82B3-27A962C46B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{2FD34A2B-33D9-4773-B5D0-6D2681A7759A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sep Updated" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sep Updated'!$A$1:$U$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sep Updated'!$A$1:$E$82</definedName>
     <definedName name="Slicer_Status">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="199">
   <si>
     <t xml:space="preserve">Teleopti ID </t>
   </si>
@@ -52,63 +52,18 @@
     <t>Login ID</t>
   </si>
   <si>
-    <t>Perm ID</t>
-  </si>
-  <si>
     <t>TTS User</t>
   </si>
   <si>
-    <t>BSS User</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
     <t>Agent Name</t>
   </si>
   <si>
-    <t>WFH Status</t>
-  </si>
-  <si>
-    <t>National ID</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>TL ID</t>
-  </si>
-  <si>
     <t>TL Name</t>
   </si>
   <si>
-    <t>1st OJT Date</t>
-  </si>
-  <si>
-    <t>1st Ops Day</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Manger ID</t>
-  </si>
-  <si>
-    <t>Manager</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>WFH Date</t>
-  </si>
-  <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>Follow - Support</t>
   </si>
   <si>
@@ -136,15 +91,6 @@
     <t>Yasmin Khaled</t>
   </si>
   <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>kareem kotp</t>
-  </si>
-  <si>
-    <t>IBS</t>
-  </si>
-  <si>
     <t>AM153769</t>
   </si>
   <si>
@@ -160,9 +106,6 @@
     <t>Aya Ebrahim Mohamed Abdelhamid</t>
   </si>
   <si>
-    <t>GPS</t>
-  </si>
-  <si>
     <t>ER104979</t>
   </si>
   <si>
@@ -214,9 +157,6 @@
     <t>Yomna Ibrahem Mahmoud Mohammed</t>
   </si>
   <si>
-    <t>X69994</t>
-  </si>
-  <si>
     <t>Mostafa.M69994</t>
   </si>
   <si>
@@ -226,9 +166,6 @@
     <t>Mostafa Mahmoud Hanafy</t>
   </si>
   <si>
-    <t>X62302</t>
-  </si>
-  <si>
     <t>Mahmoud.a.aly</t>
   </si>
   <si>
@@ -259,18 +196,12 @@
     <t>Ahmed Gomaa Mohamed Ewis</t>
   </si>
   <si>
-    <t>X61488</t>
-  </si>
-  <si>
     <t>afnan.ali</t>
   </si>
   <si>
     <t xml:space="preserve">afnan ali mohamed ahmed </t>
   </si>
   <si>
-    <t>X68854</t>
-  </si>
-  <si>
     <t>Reem.I68854</t>
   </si>
   <si>
@@ -361,27 +292,18 @@
     <t>X60379</t>
   </si>
   <si>
-    <t>x60379</t>
-  </si>
-  <si>
     <t>Muhmoud.raafat</t>
   </si>
   <si>
     <t>Mahmoud Raafat Mahmoud</t>
   </si>
   <si>
-    <t>X61782</t>
-  </si>
-  <si>
     <t>Alaa.emadahmed</t>
   </si>
   <si>
     <t>Alaa Emad Ahmed</t>
   </si>
   <si>
-    <t>X68827</t>
-  </si>
-  <si>
     <t>Aya.e68827</t>
   </si>
   <si>
@@ -451,9 +373,6 @@
     <t>Mohamed Wael Aly Mostafa</t>
   </si>
   <si>
-    <t>X70739</t>
-  </si>
-  <si>
     <t>Asmaa.A70739</t>
   </si>
   <si>
@@ -469,9 +388,6 @@
     <t xml:space="preserve">Safaa Saeed Abdelhamid Eldaly </t>
   </si>
   <si>
-    <t>X61740</t>
-  </si>
-  <si>
     <t>hend.habdelmabod</t>
   </si>
   <si>
@@ -496,9 +412,6 @@
     <t>Maternity</t>
   </si>
   <si>
-    <t>X64142</t>
-  </si>
-  <si>
     <t>sara.ali</t>
   </si>
   <si>
@@ -580,18 +493,12 @@
     <t>Mai Magdy Shawky Abdelrazek</t>
   </si>
   <si>
-    <t>X66223</t>
-  </si>
-  <si>
     <t>nagwa.h66223</t>
   </si>
   <si>
     <t>Nagwa Hesham Ismail Salama</t>
   </si>
   <si>
-    <t>X67075</t>
-  </si>
-  <si>
     <t>Maryam.M67075</t>
   </si>
   <si>
@@ -604,9 +511,6 @@
     <t>Ebram mamdoh fayez abedel shahed</t>
   </si>
   <si>
-    <t>X64483</t>
-  </si>
-  <si>
     <t>Zeinab Ahmed</t>
   </si>
   <si>
@@ -661,12 +565,6 @@
     <t>Rasha Desouki Ebrahim Abdelatef</t>
   </si>
   <si>
-    <t>WO</t>
-  </si>
-  <si>
-    <t>X65712</t>
-  </si>
-  <si>
     <t>Reham.S65712</t>
   </si>
   <si>
@@ -685,36 +583,24 @@
     <t>Ahmed Samy abdelAziz Ibrahim</t>
   </si>
   <si>
-    <t>X62389</t>
-  </si>
-  <si>
     <t>Nourhan.elgezawy</t>
   </si>
   <si>
     <t xml:space="preserve">Nourhan Atif Ali El Gezawy </t>
   </si>
   <si>
-    <t>X65812</t>
-  </si>
-  <si>
     <t>hend.e65812</t>
   </si>
   <si>
     <t>Hend Ehab Samir</t>
   </si>
   <si>
-    <t>X65849</t>
-  </si>
-  <si>
     <t>Ahmed.M65849</t>
   </si>
   <si>
     <t xml:space="preserve">Ahmed Mohamed Ibrahim Tolba </t>
   </si>
   <si>
-    <t>X66549</t>
-  </si>
-  <si>
     <t>Toka.M66549</t>
   </si>
   <si>
@@ -734,18 +620,6 @@
   </si>
   <si>
     <t>mariam gad elkareem shrab</t>
-  </si>
-  <si>
-    <t>x67708</t>
-  </si>
-  <si>
-    <t>X68835</t>
-  </si>
-  <si>
-    <t>Pro</t>
-  </si>
-  <si>
-    <t>Xceed</t>
   </si>
   <si>
     <t>Failure</t>
@@ -836,22 +710,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -870,347 +734,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="44">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1750,7 +1274,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mahmoud Seif Mohamed" refreshedDate="46281.729949652778" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="171" xr:uid="{90E536DA-20C6-4A62-B9E9-4FE74DB8F431}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:U1048576" sheet="Sep Updated"/>
+    <worksheetSource ref="A1:E1048576" sheet="Sep Updated"/>
   </cacheSource>
   <cacheFields count="26">
     <cacheField name="Teleopti ID " numFmtId="0">
@@ -7153,250 +6677,250 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>238</v>
+      <c r="A3" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>236</v>
+      <c r="A4" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7">
         <v>38</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="7">
         <v>52</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11">
+      <c r="A6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7">
         <v>17</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11">
+      <c r="A7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7">
         <v>6</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11">
+      <c r="A8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7">
         <v>4</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11">
+      <c r="A9" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7">
         <v>11</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11">
+      <c r="A10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7">
         <v>18</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11">
+      <c r="A11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7">
         <v>17</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11">
+      <c r="A12" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7">
         <v>11</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11">
+      <c r="A13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7">
         <v>6</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="11">
+      <c r="A14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="7">
         <v>30</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7">
         <v>31</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="7">
         <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11">
+      <c r="A15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7">
         <v>10</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="7">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11">
+      <c r="A16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7">
         <v>12</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="7">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="B17" s="11">
+      <c r="A17" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="7">
         <v>30</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11">
+      <c r="A18" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7">
         <v>9</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="7">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B19" s="11">
+      <c r="A19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" s="7">
         <v>30</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="7">
         <v>38</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="7">
         <v>52</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="7">
         <v>31</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="7">
         <v>151</v>
       </c>
     </row>
@@ -7415,31 +6939,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D298249-7ED6-40BA-9E05-5DFDB3CB7DCD}">
-  <dimension ref="A1:U82"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7447,4354 +6958,1734 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>73935</v>
+      </c>
+      <c r="B2" s="2">
+        <v>601492</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>68261</v>
+      </c>
+      <c r="B3" s="2">
+        <v>83957</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>216598</v>
+      </c>
+      <c r="B4" s="2">
+        <v>612110</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>199043</v>
+      </c>
+      <c r="B5" s="2">
+        <v>617242</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>250658</v>
+      </c>
+      <c r="B6" s="2">
+        <v>613147</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>59371</v>
+      </c>
+      <c r="B7" s="2">
+        <v>88077</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>60164</v>
+      </c>
+      <c r="B8" s="2">
+        <v>80398</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>65847</v>
+      </c>
+      <c r="B9" s="2">
+        <v>85210</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>219800</v>
+      </c>
+      <c r="B10" s="2">
+        <v>612892</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="F10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>153769</v>
+      </c>
+      <c r="B11" s="2">
+        <v>88870</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="3" t="s">
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="3" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>239060</v>
+      </c>
+      <c r="B12" s="2">
+        <v>614478</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="1" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>104979</v>
+      </c>
+      <c r="B13" s="3">
+        <v>612124</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>73935</v>
-      </c>
-      <c r="B2" s="4">
-        <v>601492</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>90265</v>
+      </c>
+      <c r="B14" s="2">
+        <v>85657</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>202592</v>
+      </c>
+      <c r="B15" s="2">
+        <v>617209</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>150251</v>
+      </c>
+      <c r="B16" s="2">
+        <v>608329</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>219665</v>
+      </c>
+      <c r="B17" s="2">
+        <v>612722</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>85283</v>
+      </c>
+      <c r="B18" s="2">
+        <v>609685</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>108584</v>
+      </c>
+      <c r="B19" s="2">
+        <v>80113</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>139666</v>
+      </c>
+      <c r="B20" s="2">
+        <v>613351</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>165822</v>
+      </c>
+      <c r="B21" s="2">
+        <v>601676</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>233791</v>
+      </c>
+      <c r="B22" s="2">
+        <v>613943</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="2">
+        <v>81099</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>99103</v>
+      </c>
+      <c r="B24" s="2">
+        <v>609055</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="2">
+        <v>81035</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>209678</v>
+      </c>
+      <c r="B26" s="2">
+        <v>610479</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>146619</v>
+      </c>
+      <c r="B27" s="2">
+        <v>86850</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>139586</v>
+      </c>
+      <c r="B28" s="2">
+        <v>600421</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>200410</v>
+      </c>
+      <c r="B29" s="2">
+        <v>609496</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="2">
+        <v>84095</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>137740</v>
+      </c>
+      <c r="B31" s="2">
+        <v>604296</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="2">
+        <v>80644</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>90807</v>
+      </c>
+      <c r="B33" s="2">
+        <v>609232</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>317748</v>
+      </c>
+      <c r="B34" s="2">
+        <v>635520</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="2">
+        <v>81009</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>56268</v>
+      </c>
+      <c r="B36" s="2">
+        <v>80575</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>64496</v>
+      </c>
+      <c r="B37" s="2">
+        <v>614343</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>238586</v>
+      </c>
+      <c r="B38" s="2">
+        <v>609059</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>63248</v>
+      </c>
+      <c r="B39" s="2">
+        <v>81101</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>217162</v>
+      </c>
+      <c r="B40" s="2">
+        <v>611737</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>138951</v>
+      </c>
+      <c r="B41" s="2">
+        <v>654982</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="E41" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>138163</v>
+      </c>
+      <c r="B42" s="2">
+        <v>608313</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4" t="s">
+      <c r="E42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>230149</v>
+      </c>
+      <c r="B43" s="2">
+        <v>612279</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>236380</v>
+      </c>
+      <c r="B44" s="2">
+        <v>612481</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>237293</v>
+      </c>
+      <c r="B45" s="2">
+        <v>611386</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>376127</v>
+      </c>
+      <c r="B46" s="2">
+        <v>656667</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>155947</v>
+      </c>
+      <c r="B47" s="2">
+        <v>81023</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>222804</v>
+      </c>
+      <c r="B48" s="2">
+        <v>613674</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>195261</v>
+      </c>
+      <c r="B49" s="2">
+        <v>604421</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>245551</v>
+      </c>
+      <c r="B50" s="2">
+        <v>611310</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>218826</v>
+      </c>
+      <c r="B51" s="2">
+        <v>610586</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>212948</v>
+      </c>
+      <c r="B52" s="2">
+        <v>611713</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="21.75" x14ac:dyDescent="0.6">
+      <c r="A53" s="2">
+        <v>237914</v>
+      </c>
+      <c r="B53" s="8">
+        <v>613928</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>288176</v>
+      </c>
+      <c r="B54" s="2">
+        <v>634113</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>341801</v>
+      </c>
+      <c r="B55" s="2">
+        <v>656661</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>322968</v>
+      </c>
+      <c r="B56" s="2">
+        <v>656663</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>405564</v>
+      </c>
+      <c r="B57" s="2">
+        <v>656668</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>370864</v>
+      </c>
+      <c r="B58" s="2">
+        <v>656665</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>163187</v>
+      </c>
+      <c r="B59" s="2">
+        <v>657219</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>405513</v>
+      </c>
+      <c r="B60" s="2">
+        <v>656672</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>405535</v>
+      </c>
+      <c r="B61" s="2">
+        <v>656674</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>204903</v>
+      </c>
+      <c r="B62" s="2">
+        <v>657217</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>219531</v>
+      </c>
+      <c r="B63" s="2">
+        <v>89152</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>68261</v>
-      </c>
-      <c r="B3" s="4">
-        <v>83957</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4" t="s">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>219539</v>
+      </c>
+      <c r="B64" s="2">
+        <v>609473</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="5"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>216598</v>
-      </c>
-      <c r="B4" s="4">
-        <v>612110</v>
-      </c>
-      <c r="C4" s="4">
-        <v>216598</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4" t="s">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>152746</v>
+      </c>
+      <c r="B65" s="2">
+        <v>609439</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>224584</v>
+      </c>
+      <c r="B66" s="2">
+        <v>609054</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>50067</v>
+      </c>
+      <c r="B67" s="2">
+        <v>81262</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>129179</v>
+      </c>
+      <c r="B68" s="2">
+        <v>609552</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>78409</v>
+      </c>
+      <c r="B69" s="2">
+        <v>81412</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>208009</v>
+      </c>
+      <c r="B70" s="2">
+        <v>653434</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>212027</v>
+      </c>
+      <c r="B71" s="2">
+        <v>609517</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="5"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>199043</v>
-      </c>
-      <c r="B5" s="4">
-        <v>617242</v>
-      </c>
-      <c r="C5" s="4">
-        <v>199043</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4" t="s">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" s="2">
+        <v>80624</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="5"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>250658</v>
-      </c>
-      <c r="B6" s="4">
-        <v>613147</v>
-      </c>
-      <c r="C6" s="4">
-        <v>250658</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U6" s="5"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>59371</v>
-      </c>
-      <c r="B7" s="4">
-        <v>88077</v>
-      </c>
-      <c r="C7" s="4">
-        <v>14205</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4" t="s">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>225232</v>
+      </c>
+      <c r="B73" s="2">
+        <v>606553</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>156958</v>
+      </c>
+      <c r="B74" s="2">
+        <v>86466</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>274533</v>
+      </c>
+      <c r="B75" s="2">
+        <v>656671</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>317858</v>
+      </c>
+      <c r="B76" s="2">
+        <v>635996</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>340073</v>
+      </c>
+      <c r="B77" s="2">
+        <v>656662</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>298534</v>
+      </c>
+      <c r="B78" s="2">
+        <v>619694</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>181272</v>
+      </c>
+      <c r="B79" s="2">
+        <v>604193</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>207507</v>
+      </c>
+      <c r="B80" s="2">
+        <v>609846</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" s="2">
+        <v>612283</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U7" s="5"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>60164</v>
-      </c>
-      <c r="B8" s="4">
-        <v>80398</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U8" s="5"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>65847</v>
-      </c>
-      <c r="B9" s="4">
-        <v>85210</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N9" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U9" s="5"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>219800</v>
-      </c>
-      <c r="B10" s="4">
-        <v>612892</v>
-      </c>
-      <c r="C10" s="4">
-        <v>219800</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U10" s="5"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>153769</v>
-      </c>
-      <c r="B11" s="4">
-        <v>88870</v>
-      </c>
-      <c r="C11" s="4">
-        <v>25372</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U11" s="5"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
-        <v>239060</v>
-      </c>
-      <c r="B12" s="4">
-        <v>614478</v>
-      </c>
-      <c r="C12" s="4">
-        <v>239060</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N12" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U12" s="5"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>104979</v>
-      </c>
-      <c r="B13" s="7">
-        <v>612124</v>
-      </c>
-      <c r="C13" s="4">
-        <v>104979</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N13" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U13" s="5"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
-        <v>90265</v>
-      </c>
-      <c r="B14" s="4">
-        <v>85657</v>
-      </c>
-      <c r="C14" s="4">
-        <v>16982</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N14" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U14" s="5"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
-        <v>202592</v>
-      </c>
-      <c r="B15" s="4">
-        <v>617209</v>
-      </c>
-      <c r="C15" s="4">
-        <v>202592</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U15" s="5"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>150251</v>
-      </c>
-      <c r="B16" s="4">
-        <v>608329</v>
-      </c>
-      <c r="C16" s="4">
-        <v>24777</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U16" s="5"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
-        <v>219665</v>
-      </c>
-      <c r="B17" s="4">
-        <v>612722</v>
-      </c>
-      <c r="C17" s="4">
-        <v>219665</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U17" s="5"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
-        <v>85283</v>
-      </c>
-      <c r="B18" s="4">
-        <v>609685</v>
-      </c>
-      <c r="C18" s="4">
-        <v>85283</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N18" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U18" s="5"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
-        <v>108584</v>
-      </c>
-      <c r="B19" s="4">
-        <v>80113</v>
-      </c>
-      <c r="C19" s="4">
-        <v>20778</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N19" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U19" s="5"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
-        <v>139666</v>
-      </c>
-      <c r="B20" s="4">
-        <v>613351</v>
-      </c>
-      <c r="C20" s="4">
-        <v>139666</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="4">
-        <v>93748</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N20" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U20" s="5"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
-        <v>165822</v>
-      </c>
-      <c r="B21" s="4">
-        <v>601676</v>
-      </c>
-      <c r="C21" s="4">
-        <v>165822</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N21" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U21" s="5"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
-        <v>233791</v>
-      </c>
-      <c r="B22" s="4">
-        <v>613943</v>
-      </c>
-      <c r="C22" s="4">
-        <v>233791</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N22" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U22" s="5"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B23" s="4">
-        <v>81099</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N23" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U23" s="5"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
-        <v>99103</v>
-      </c>
-      <c r="B24" s="4">
-        <v>609055</v>
-      </c>
-      <c r="C24" s="4">
-        <v>29593</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N24" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U24" s="5"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="4">
-        <v>81035</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N25" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U25" s="5"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
-        <v>209678</v>
-      </c>
-      <c r="B26" s="4">
-        <v>610479</v>
-      </c>
-      <c r="C26" s="4">
-        <v>209678</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U26" s="5"/>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
-        <v>146619</v>
-      </c>
-      <c r="B27" s="4">
-        <v>86850</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N27" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U27" s="5"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
-        <v>139586</v>
-      </c>
-      <c r="B28" s="4">
-        <v>600421</v>
-      </c>
-      <c r="C28" s="4">
-        <v>23854</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N28" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U28" s="5"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
-        <v>200410</v>
-      </c>
-      <c r="B29" s="4">
-        <v>609496</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N29" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U29" s="5"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="4">
-        <v>84095</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I30" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N30" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U30" s="5"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
-        <v>137740</v>
-      </c>
-      <c r="B31" s="4">
-        <v>604296</v>
-      </c>
-      <c r="C31" s="4">
-        <v>28087</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N31" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="U31" s="5"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="4">
-        <v>80644</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="I32" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N32" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U32" s="5"/>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
-        <v>90807</v>
-      </c>
-      <c r="B33" s="4">
-        <v>609232</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I33" s="4">
-        <v>24588</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N33" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U33" s="5"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
-        <v>317748</v>
-      </c>
-      <c r="B34" s="4">
-        <v>635520</v>
-      </c>
-      <c r="C34" s="4">
-        <v>317748</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N34" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O34" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U34" s="5"/>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="4">
-        <v>81009</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N35" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O35" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U35" s="5"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>56268</v>
-      </c>
-      <c r="B36" s="4">
-        <v>80575</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N36" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U36" s="5"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
-        <v>64496</v>
-      </c>
-      <c r="B37" s="4">
-        <v>614343</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N37" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O37" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U37" s="5"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
-        <v>238586</v>
-      </c>
-      <c r="B38" s="4">
-        <v>609059</v>
-      </c>
-      <c r="C38" s="4">
-        <v>238586</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I38" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N38" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O38" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U38" s="5"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
-        <v>63248</v>
-      </c>
-      <c r="B39" s="4">
-        <v>81101</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="4">
-        <v>15198</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N39" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U39" s="5"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
-        <v>217162</v>
-      </c>
-      <c r="B40" s="4">
-        <v>611737</v>
-      </c>
-      <c r="C40" s="4">
-        <v>217162</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N40" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U40" s="5"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
-        <v>138951</v>
-      </c>
-      <c r="B41" s="4">
-        <v>654982</v>
-      </c>
-      <c r="C41" s="4">
-        <v>23349</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N41" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U41" s="5"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
-        <v>138163</v>
-      </c>
-      <c r="B42" s="4">
-        <v>608313</v>
-      </c>
-      <c r="C42" s="4">
-        <v>23313</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N42" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O42" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U42" s="5"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
-        <v>230149</v>
-      </c>
-      <c r="B43" s="4">
-        <v>612279</v>
-      </c>
-      <c r="C43" s="4">
-        <v>230149</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N43" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O43" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U43" s="5"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
-        <v>236380</v>
-      </c>
-      <c r="B44" s="4">
-        <v>612481</v>
-      </c>
-      <c r="C44" s="4">
-        <v>236380</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N44" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O44" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U44" s="5"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
-        <v>237293</v>
-      </c>
-      <c r="B45" s="4">
-        <v>611386</v>
-      </c>
-      <c r="C45" s="4">
-        <v>237293</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I45" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N45" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O45" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U45" s="5"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
-        <v>376127</v>
-      </c>
-      <c r="B46" s="4">
-        <v>656667</v>
-      </c>
-      <c r="C46" s="4">
-        <v>376127</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="4">
-        <v>15198</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N46" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U46" s="5"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
-        <v>155947</v>
-      </c>
-      <c r="B47" s="4">
-        <v>81023</v>
-      </c>
-      <c r="C47" s="4">
-        <v>26104</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I47" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N47" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O47" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U47" s="5"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
-        <v>222804</v>
-      </c>
-      <c r="B48" s="4">
-        <v>613674</v>
-      </c>
-      <c r="C48" s="4">
-        <v>222804</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I48" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N48" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O48" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U48" s="5"/>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
-        <v>195261</v>
-      </c>
-      <c r="B49" s="4">
-        <v>604421</v>
-      </c>
-      <c r="C49" s="4">
-        <v>30173</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N49" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O49" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U49" s="5"/>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
-        <v>245551</v>
-      </c>
-      <c r="B50" s="4">
-        <v>611310</v>
-      </c>
-      <c r="C50" s="4">
-        <v>245551</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N50" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O50" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U50" s="5"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
-        <v>218826</v>
-      </c>
-      <c r="B51" s="4">
-        <v>610586</v>
-      </c>
-      <c r="C51" s="4">
-        <v>218826</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" s="4">
-        <v>24181</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N51" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O51" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U51" s="5"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
-        <v>212948</v>
-      </c>
-      <c r="B52" s="4">
-        <v>611713</v>
-      </c>
-      <c r="C52" s="4">
-        <v>212948</v>
-      </c>
-      <c r="D52" s="4" t="s">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>69619</v>
+      </c>
+      <c r="B82" s="2">
+        <v>81326</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N52" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O52" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U52" s="5"/>
-    </row>
-    <row r="53" spans="1:21" ht="21.75" x14ac:dyDescent="0.6">
-      <c r="A53" s="4">
-        <v>237914</v>
-      </c>
-      <c r="B53" s="12">
-        <v>613928</v>
-      </c>
-      <c r="C53" s="4">
-        <v>237914</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N53" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O53" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U53" s="5"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
-        <v>288176</v>
-      </c>
-      <c r="B54" s="4">
-        <v>634113</v>
-      </c>
-      <c r="C54" s="4">
-        <v>288176</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N54" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O54" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U54" s="5"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
-        <v>341801</v>
-      </c>
-      <c r="B55" s="4">
-        <v>656661</v>
-      </c>
-      <c r="C55" s="4">
-        <v>341801</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N55" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O55" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U55" s="5"/>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
-        <v>322968</v>
-      </c>
-      <c r="B56" s="4">
-        <v>656663</v>
-      </c>
-      <c r="C56" s="4">
-        <v>322968</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N56" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O56" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U56" s="5"/>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
-        <v>405564</v>
-      </c>
-      <c r="B57" s="4">
-        <v>656668</v>
-      </c>
-      <c r="C57" s="4">
-        <v>405564</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I57" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N57" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O57" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U57" s="5"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
-        <v>370864</v>
-      </c>
-      <c r="B58" s="4">
-        <v>656665</v>
-      </c>
-      <c r="C58" s="4">
-        <v>370864</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I58" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N58" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O58" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U58" s="5"/>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
-        <v>163187</v>
-      </c>
-      <c r="B59" s="4">
-        <v>657219</v>
-      </c>
-      <c r="C59" s="4">
-        <v>163187</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I59" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N59" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O59" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U59" s="5"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
-        <v>405513</v>
-      </c>
-      <c r="B60" s="4">
-        <v>656672</v>
-      </c>
-      <c r="C60" s="4">
-        <v>405513</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I60" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N60" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O60" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U60" s="5"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>405535</v>
-      </c>
-      <c r="B61" s="4">
-        <v>656674</v>
-      </c>
-      <c r="C61" s="4">
-        <v>405535</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N61" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O61" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U61" s="5"/>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>204903</v>
-      </c>
-      <c r="B62" s="4">
-        <v>657217</v>
-      </c>
-      <c r="C62" s="4">
-        <v>204903</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I62" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N62" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O62" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U62" s="5"/>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>219531</v>
-      </c>
-      <c r="B63" s="4">
-        <v>89152</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I63" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N63" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U63" s="5"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>219539</v>
-      </c>
-      <c r="B64" s="4">
-        <v>609473</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I64" s="4">
-        <v>237449</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N64" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O64" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P64" s="6"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U64" s="5"/>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>152746</v>
-      </c>
-      <c r="B65" s="4">
-        <v>609439</v>
-      </c>
-      <c r="C65" s="4">
-        <v>26820</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N65" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O65" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U65" s="5"/>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>224584</v>
-      </c>
-      <c r="B66" s="4">
-        <v>609054</v>
-      </c>
-      <c r="C66" s="4">
-        <v>224584</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N66" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O66" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P66" s="6"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U66" s="5"/>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>50067</v>
-      </c>
-      <c r="B67" s="4">
-        <v>81262</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5"/>
-      <c r="M67" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N67" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O67" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P67" s="6"/>
-      <c r="Q67" s="6"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U67" s="5"/>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>129179</v>
-      </c>
-      <c r="B68" s="4">
-        <v>609552</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N68" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O68" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P68" s="6"/>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U68" s="5"/>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>78409</v>
-      </c>
-      <c r="B69" s="4">
-        <v>81412</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N69" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O69" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P69" s="6"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U69" s="5"/>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>208009</v>
-      </c>
-      <c r="B70" s="4">
-        <v>653434</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N70" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O70" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U70" s="5"/>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
-        <v>212027</v>
-      </c>
-      <c r="B71" s="4">
-        <v>609517</v>
-      </c>
-      <c r="C71" s="4">
-        <v>212027</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N71" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O71" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P71" s="6"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U71" s="5"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A72" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B72" s="4">
-        <v>80624</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N72" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O72" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U72" s="5"/>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
-        <v>225232</v>
-      </c>
-      <c r="B73" s="4">
-        <v>606553</v>
-      </c>
-      <c r="C73" s="4">
-        <v>225232</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K73" s="5"/>
-      <c r="L73" s="5"/>
-      <c r="M73" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N73" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O73" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P73" s="6"/>
-      <c r="Q73" s="6"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U73" s="5"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
-        <v>156958</v>
-      </c>
-      <c r="B74" s="4">
-        <v>86466</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N74" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O74" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P74" s="6"/>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U74" s="5"/>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
-        <v>274533</v>
-      </c>
-      <c r="B75" s="4">
-        <v>656671</v>
-      </c>
-      <c r="C75" s="4">
-        <v>274533</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K75" s="5"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N75" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O75" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P75" s="6"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U75" s="5"/>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A76" s="4">
-        <v>317858</v>
-      </c>
-      <c r="B76" s="4">
-        <v>635996</v>
-      </c>
-      <c r="C76" s="4">
-        <v>317858</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
-      <c r="M76" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N76" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O76" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P76" s="6"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U76" s="5"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A77" s="4">
-        <v>340073</v>
-      </c>
-      <c r="B77" s="4">
-        <v>656662</v>
-      </c>
-      <c r="C77" s="4">
-        <v>340073</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K77" s="5"/>
-      <c r="L77" s="5"/>
-      <c r="M77" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N77" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O77" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P77" s="6"/>
-      <c r="Q77" s="6"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U77" s="5"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A78" s="4">
-        <v>298534</v>
-      </c>
-      <c r="B78" s="4">
-        <v>619694</v>
-      </c>
-      <c r="C78" s="4">
-        <v>298534</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K78" s="5"/>
-      <c r="L78" s="5"/>
-      <c r="M78" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N78" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O78" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P78" s="6"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="U78" s="5"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A79" s="4">
-        <v>181272</v>
-      </c>
-      <c r="B79" s="4">
-        <v>604193</v>
-      </c>
-      <c r="C79" s="4">
-        <v>27656</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K79" s="5"/>
-      <c r="L79" s="5"/>
-      <c r="M79" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N79" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O79" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P79" s="6"/>
-      <c r="Q79" s="6"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U79" s="5"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A80" s="4">
-        <v>207507</v>
-      </c>
-      <c r="B80" s="4">
-        <v>609846</v>
-      </c>
-      <c r="C80" s="4">
-        <v>207507</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K80" s="5"/>
-      <c r="L80" s="5"/>
-      <c r="M80" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N80" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P80" s="6"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
-      <c r="T80" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U80" s="5"/>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A81" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B81" s="4">
-        <v>612283</v>
-      </c>
-      <c r="C81" s="4">
-        <v>84014</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J81" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K81" s="5"/>
-      <c r="L81" s="5"/>
-      <c r="M81" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N81" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O81" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P81" s="6"/>
-      <c r="Q81" s="6"/>
-      <c r="R81" s="4"/>
-      <c r="S81" s="4"/>
-      <c r="T81" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="U81" s="5"/>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A82" s="4">
-        <v>69619</v>
-      </c>
-      <c r="B82" s="4">
-        <v>81326</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K82" s="5"/>
-      <c r="L82" s="5"/>
-      <c r="M82" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N82" s="7">
-        <v>36748</v>
-      </c>
-      <c r="O82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P82" s="6"/>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-      <c r="T82" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U82" s="5"/>
+      <c r="F82" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U82" xr:uid="{1D298249-7ED6-40BA-9E05-5DFDB3CB7DCD}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U82">
-      <sortCondition ref="J1:J82"/>
+  <autoFilter ref="A1:E82" xr:uid="{1D298249-7ED6-40BA-9E05-5DFDB3CB7DCD}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E82">
+      <sortCondition ref="E1:E82"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="77" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="75" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="72" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="66" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="63" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="62" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="59" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="57" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="duplicateValues" dxfId="54" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="53" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="51" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="48" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="96"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="43" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="39" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="38" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A33">
-    <cfRule type="duplicateValues" dxfId="37" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="duplicateValues" dxfId="36" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24:E33">
-    <cfRule type="duplicateValues" dxfId="35" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="duplicateValues" dxfId="25" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="duplicateValues" dxfId="20" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10:D17">
-    <cfRule type="duplicateValues" dxfId="16" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:A43">
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C41:C43">
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:A51">
-    <cfRule type="duplicateValues" dxfId="13" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:A51">
-    <cfRule type="duplicateValues" dxfId="12" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:A51">
-    <cfRule type="duplicateValues" dxfId="10" priority="105"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C44:C51">
-    <cfRule type="duplicateValues" dxfId="9" priority="106"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C41:C51">
-    <cfRule type="duplicateValues" dxfId="8" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="108"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C41:C51">
-    <cfRule type="duplicateValues" dxfId="6" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:A82">
-    <cfRule type="duplicateValues" dxfId="5" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52:B82">
-    <cfRule type="duplicateValues" dxfId="4" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="3" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="2" priority="114"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
-    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048398">
     <cfRule type="duplicateValues" dxfId="0" priority="116"/>
